--- a/task133/golden/ecl_allowance_2026Q3.xlsx
+++ b/task133/golden/ecl_allowance_2026Q3.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4661FDBB-36CC-43F5-8CF7-A04ACE50324F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{323D4226-340B-4BE4-8817-7665168AFBBF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{323D4226-340B-4BE4-8817-7665168AFBBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Allowance" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
     <t>Stage 2: 30 or more days past due, a hardship arrangement in force on 30 September 2026 (start on or before, end on or after, not cancelled), or a behaviour score 60 or more points below origination on scorecard v4; v3 origination scores converted as 1.12 x v3 - 18, rounded (section 2 and the June 2024 migration note).</t>
   </si>
   <si>
-    <t>PD(k) is (C(a+k) - C(a+k-1)) / (1 - C(a)) on the PLPD-2026.06 curve for the loan's product, where a is the number of monthly repayments fallen due by 30 September: the curve runs from origination, and a performing loan has already come through its first a months.</t>
+    <t>PD(k) is (C(a+k) - C(a+k-1)) / (1 - C(a)) on the PLPD-2026.06 curve for the loan's product, where a is the number of monthly repayments fallen due by 30 September: the curve runs from origination, and a performing loan has already come through its first a months. A loan past its contractual maturity outside stage 3 has one remaining month (section 3.2), the last month of its product's curve.</t>
   </si>
   <si>
     <t>EAD re-amortises the current balance over the remaining term at the contract rate; months discounted at the contract rate; LGD 70 per cent PL36, 76 per cent PL60 (sections 3.3 to 3.5).</t>
@@ -168,7 +168,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E2B3C"/>
+        <fgColor rgb="FF1E2B3C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -511,12 +511,12 @@
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -526,7 +526,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4">
-        <v>13667000</v>
+        <v>13773000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -534,7 +534,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="5">
-        <v>10958000</v>
+        <v>10933000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -542,7 +542,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="5">
-        <v>2709000</v>
+        <v>2840000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -558,7 +558,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="7">
-        <v>363</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -608,16 +608,16 @@
         <v>14</v>
       </c>
       <c r="C2" s="7">
-        <v>17157</v>
+        <v>17109</v>
       </c>
       <c r="D2" s="5">
-        <v>138511000</v>
+        <v>138349000</v>
       </c>
       <c r="E2" s="5">
-        <v>3217000</v>
+        <v>3202000</v>
       </c>
       <c r="F2" s="9">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -628,16 +628,16 @@
         <v>15</v>
       </c>
       <c r="C3" s="7">
-        <v>20055</v>
+        <v>20180</v>
       </c>
       <c r="D3" s="5">
-        <v>329546000</v>
+        <v>330436000</v>
       </c>
       <c r="E3" s="5">
-        <v>7740000</v>
+        <v>7731000</v>
       </c>
       <c r="F3" s="9">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -648,16 +648,16 @@
         <v>14</v>
       </c>
       <c r="C4" s="7">
-        <v>1406</v>
+        <v>1421</v>
       </c>
       <c r="D4" s="5">
-        <v>11229000</v>
+        <v>11728000</v>
       </c>
       <c r="E4" s="5">
-        <v>673000</v>
+        <v>681000</v>
       </c>
       <c r="F4" s="9">
-        <v>5.99</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -668,16 +668,16 @@
         <v>15</v>
       </c>
       <c r="C5" s="7">
-        <v>1714</v>
+        <v>1844</v>
       </c>
       <c r="D5" s="5">
-        <v>26379000</v>
+        <v>28735000</v>
       </c>
       <c r="E5" s="5">
-        <v>2036000</v>
+        <v>2159000</v>
       </c>
       <c r="F5" s="9">
-        <v>7.72</v>
+        <v>7.51</v>
       </c>
     </row>
   </sheetData>
@@ -715,7 +715,7 @@
         <v>5000</v>
       </c>
       <c r="C2" s="5">
-        <v>599000</v>
+        <v>641000</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -723,10 +723,10 @@
         <v>21</v>
       </c>
       <c r="B3" s="5">
-        <v>158000</v>
+        <v>159000</v>
       </c>
       <c r="C3" s="5">
-        <v>1054000</v>
+        <v>1073000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -734,10 +734,10 @@
         <v>22</v>
       </c>
       <c r="B4" s="5">
-        <v>896000</v>
+        <v>940000</v>
       </c>
       <c r="C4" s="5">
-        <v>2443000</v>
+        <v>2412000</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -745,10 +745,10 @@
         <v>23</v>
       </c>
       <c r="B5" s="5">
-        <v>2832000</v>
+        <v>2779000</v>
       </c>
       <c r="C5" s="5">
-        <v>5680000</v>
+        <v>5763000</v>
       </c>
     </row>
   </sheetData>

--- a/task133/golden/ecl_allowance_2026Q3.xlsx
+++ b/task133/golden/ecl_allowance_2026Q3.xlsx
@@ -98,7 +98,7 @@
     <t>Stage 2: 30 or more days past due, a hardship arrangement in force on 30 September 2026 (start on or before, end on or after, not cancelled), or a behaviour score 60 or more points below origination on scorecard v4; v3 origination scores converted as 1.12 x v3 - 18, rounded (section 2 and the June 2024 migration note).</t>
   </si>
   <si>
-    <t>PD(k) is (C(a+k) - C(a+k-1)) / (1 - C(a)) on the PLPD-2026.06 curve for the loan's product, where a is the number of monthly repayments fallen due by 30 September: the curve runs from origination, and a performing loan has already come through its first a months. A loan past its contractual maturity outside stage 3 has one remaining month (section 3.2), the last month of its product's curve.</t>
+    <t>PD(k) is (C(a+k) - C(a+k-1)) / (1 - C(a)) on the PLPD-2026.06 curve for the loan's product, where a is the number of monthly repayments fallen due by 30 September, repayment dates in a payment pause included: the curve runs from origination, and a performing loan has already come through its first a months. A loan past its contractual maturity outside stage 3 is in the final month of its term with one month remaining (section 3.2), the last month of its product's curve.</t>
   </si>
   <si>
     <t>EAD re-amortises the current balance over the remaining term at the contract rate; months discounted at the contract rate; LGD 70 per cent PL36, 76 per cent PL60 (sections 3.3 to 3.5).</t>
@@ -230,34 +230,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -265,9 +265,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -294,14 +294,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -328,6 +346,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -339,166 +375,142 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 

--- a/task133/golden/ecl_allowance_2026Q3.xlsx
+++ b/task133/golden/ecl_allowance_2026Q3.xlsx
@@ -9,21 +9,21 @@
   </bookViews>
   <sheets>
     <sheet name="Allowance" sheetId="1" r:id="rId1"/>
-    <sheet name="Stage and product" sheetId="2" r:id="rId2"/>
-    <sheet name="By drawdown year" sheetId="3" r:id="rId3"/>
-    <sheet name="Notes" sheetId="4" r:id="rId4"/>
+    <sheet name="Realised LGD" sheetId="2" r:id="rId2"/>
+    <sheet name="Stage migration" sheetId="3" r:id="rId3"/>
+    <sheet name="Method" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
   <si>
     <t>Personal loans (PL36, PL60): collective ECL allowance at 30 September 2026</t>
   </si>
   <si>
-    <t>Credit Risk Reporting, 9 October 2026. CRM-ECL-04 v4.1; scenarios approved 18 September 2026.</t>
+    <t>Credit Risk Reporting, 9 October 2026. CRM-ECL-04 v4.2; scenarios approved 18 September 2026.</t>
   </si>
   <si>
     <t>Collective ECL allowance (AUD)</t>
@@ -35,79 +35,100 @@
     <t>Stage 2 allowance (AUD)</t>
   </si>
   <si>
+    <t>Loans in stage 1</t>
+  </si>
+  <si>
+    <t>Loans in stage 2</t>
+  </si>
+  <si>
+    <t>Loans in stage 3, assessed under CRM-ECL-06</t>
+  </si>
+  <si>
     <t>Probability-weighted PD multiplier</t>
   </si>
   <si>
-    <t>Loans in stage 3, outside the collective model</t>
-  </si>
-  <si>
-    <t>Stage</t>
+    <t>Source: loan system extract ECL_QE_BOOK at close of business 30 September 2026 (run 1 October); PLPD-2026.06 curve and development sample; Q1 FY27 scenario sheet.</t>
+  </si>
+  <si>
+    <t>2023-24 defaults: share of the balance at default not recovered, at 30 September 2026 (CRM-ECL-04 3.3)</t>
   </si>
   <si>
     <t>Product</t>
   </si>
   <si>
+    <t>Quarter of default</t>
+  </si>
+  <si>
     <t>Loans</t>
   </si>
   <si>
-    <t>Gross carrying amount (AUD)</t>
-  </si>
-  <si>
-    <t>Allowance (AUD)</t>
-  </si>
-  <si>
-    <t>Coverage (%)</t>
+    <t>Balance at default (AUD)</t>
+  </si>
+  <si>
+    <t>Realised loss (%)</t>
+  </si>
+  <si>
+    <t>LGD in use (%)</t>
+  </si>
+  <si>
+    <t>PL36</t>
+  </si>
+  <si>
+    <t>Jul to Sep 2023</t>
+  </si>
+  <si>
+    <t>Oct to Dec 2023</t>
+  </si>
+  <si>
+    <t>Jan to Mar 2024</t>
+  </si>
+  <si>
+    <t>Apr to Jun 2024</t>
+  </si>
+  <si>
+    <t>PL60</t>
+  </si>
+  <si>
+    <t>Loans in stage 1 or 2 at 30 June 2026: where they stand at 30 September 2026</t>
+  </si>
+  <si>
+    <t>Stage at 30 June</t>
   </si>
   <si>
     <t>Stage 1</t>
   </si>
   <si>
-    <t>PL36</t>
-  </si>
-  <si>
-    <t>PL60</t>
-  </si>
-  <si>
     <t>Stage 2</t>
   </si>
   <si>
-    <t>Drawdown year</t>
-  </si>
-  <si>
-    <t>PL36 allowance (AUD)</t>
-  </si>
-  <si>
-    <t>PL60 allowance (AUD)</t>
-  </si>
-  <si>
-    <t>2023 and earlier</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>Scope: PL36 and PL60 loans open in the loan system at close of business 30 September 2026; loans 90 or more days past due are stage 3 and sit under CRM-ECL-06 (CRM-ECL-04 section 1).</t>
-  </si>
-  <si>
-    <t>Stage 2: 30 or more days past due, a hardship arrangement in force on 30 September 2026 (start on or before, end on or after, not cancelled), or a behaviour score 60 or more points below origination on scorecard v4; v3 origination scores converted as 1.12 x v3 - 18, rounded (section 2 and the June 2024 migration note).</t>
-  </si>
-  <si>
-    <t>PD(k) is (C(a+k) - C(a+k-1)) / (1 - C(a)) on the PLPD-2026.06 curve for the loan's product, where a is the number of monthly repayments fallen due by 30 September, repayment dates in a payment pause included: the curve runs from origination, and a performing loan has already come through its first a months. A loan past its contractual maturity outside stage 3 is in the final month of its term with one month remaining (section 3.2), the last month of its product's curve.</t>
-  </si>
-  <si>
-    <t>EAD re-amortises the current balance over the remaining term at the contract rate; months discounted at the contract rate; LGD 70 per cent PL36, 76 per cent PL60 (sections 3.3 to 3.5).</t>
-  </si>
-  <si>
-    <t>Scenario weights 55 / 30 / 15 per cent on PD multipliers 1.00 / 1.30 / 0.80 give a weighted multiplier of 1.0600 (section 4).</t>
-  </si>
-  <si>
-    <t>Amounts are rounded to the nearest thousand dollars from unrounded loan-level results, so rows may not add exactly.</t>
+    <t>Stage 3</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Loans at 30 June</t>
+  </si>
+  <si>
+    <t>Stage at 30 September under CRM-ECL-04 section 2; closed means repaid, settled or written off by then.</t>
+  </si>
+  <si>
+    <t>Scope: PL36 and PL60 loans open at close of business 30 September 2026. Loans 90 or more days past due are stage 3 and are assessed under CRM-ECL-06.</t>
+  </si>
+  <si>
+    <t>Stage 2: 30 or more days past due, a hardship arrangement in force on the date (start to end, both included, not from the day it is cancelled), or a behaviour score 60 or more points below origination on v4 from the month-end run on the position at the date; v3 origination scores converted as 1.12 x v3 - 18, rounded. At 30 June the June month-end run (made 1 July) supplies the scores.</t>
+  </si>
+  <si>
+    <t>PD(k): the PLPD-2026.06 curve gives, for every loan drawn in the development window, the share defaulted by each month on book. A loan a months on book that is still open and has not defaulted takes (C(a+k) - C(a+k-1)) / S(a), where S(a) is the share of the development sample still open and never defaulted at the end of month a (1 - C(a) less the share repaid in full by then). Stage 2 PD carries the 2.4 scalar. A loan past its maturity outside stage 3 has one month remaining (3.2).</t>
+  </si>
+  <si>
+    <t>EAD re-amortises the current balance over the remaining term at the contract rate; each month is discounted at the contract rate; LGD 70 per cent PL36, 76 per cent PL60; scenarios 55 / 30 / 15 per cent on multipliers 1.00 / 1.30 / 0.80 (weighted 1.06).</t>
+  </si>
+  <si>
+    <t>Realised loss (3.3): receipts after default to 30 September 2026 from the Collections receipts file, plus each sold account's share of the March 2026 sale (face value at cut-off x 3.85 cents), each taken at the end of the month received and discounted to the default month end at the contract rate; cured loans lose nothing.</t>
+  </si>
+  <si>
+    <t>Amounts are rounded to the nearest thousand dollars from loan-level results, so stage amounts may not add exactly.</t>
   </si>
 </sst>
 </file>
@@ -116,9 +137,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,6 +166,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -185,20 +214,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -516,11 +547,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECEF707-7CC3-4602-830C-06AB2E21172D}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="46.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -538,7 +569,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4">
-        <v>13773000</v>
+        <v>13160000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -546,7 +577,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="5">
-        <v>10933000</v>
+        <v>10563000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -554,23 +585,44 @@
         <v>4</v>
       </c>
       <c r="B6" s="5">
-        <v>2840000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6">
-        <v>1.06</v>
+        <v>2597000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6">
+        <v>37288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B9" s="6">
+        <v>3266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6">
         <v>343</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -581,115 +633,200 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A7C7CA4-85C6-4ECD-8D37-C64D13DD0CB9}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="8" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="7">
-        <v>17109</v>
-      </c>
-      <c r="D2" s="5">
-        <v>138349000</v>
-      </c>
-      <c r="E2" s="5">
-        <v>3202000</v>
-      </c>
-      <c r="F2" s="9">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="7">
-        <v>20180</v>
-      </c>
-      <c r="D3" s="5">
-        <v>330436000</v>
-      </c>
-      <c r="E3" s="5">
-        <v>7731000</v>
-      </c>
-      <c r="F3" s="9">
-        <v>2.34</v>
+      <c r="F3" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="7">
-        <v>1421</v>
-      </c>
-      <c r="D4" s="5">
-        <v>11728000</v>
-      </c>
-      <c r="E4" s="5">
-        <v>681000</v>
-      </c>
-      <c r="F4" s="9">
-        <v>5.81</v>
+        <v>18</v>
+      </c>
+      <c r="C4" s="6">
+        <v>142</v>
+      </c>
+      <c r="D4" s="10">
+        <v>1445693.9</v>
+      </c>
+      <c r="E4" s="11">
+        <v>67.9</v>
+      </c>
+      <c r="F4" s="12">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="7">
-        <v>1844</v>
-      </c>
-      <c r="D5" s="5">
-        <v>28735000</v>
-      </c>
-      <c r="E5" s="5">
-        <v>2159000</v>
-      </c>
-      <c r="F5" s="9">
-        <v>7.51</v>
+        <v>19</v>
+      </c>
+      <c r="C5" s="6">
+        <v>139</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1489194.03</v>
+      </c>
+      <c r="E5" s="11">
+        <v>65.8</v>
+      </c>
+      <c r="F5" s="12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="6">
+        <v>164</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1825983.96</v>
+      </c>
+      <c r="E6" s="11">
+        <v>70.7</v>
+      </c>
+      <c r="F6" s="12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="6">
+        <v>144</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1486050.53</v>
+      </c>
+      <c r="E7" s="11">
+        <v>70.9</v>
+      </c>
+      <c r="F7" s="12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6">
+        <v>119</v>
+      </c>
+      <c r="D8" s="10">
+        <v>3016811.56</v>
+      </c>
+      <c r="E8" s="11">
+        <v>70.4</v>
+      </c>
+      <c r="F8" s="12">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="6">
+        <v>126</v>
+      </c>
+      <c r="D9" s="10">
+        <v>2751515.5</v>
+      </c>
+      <c r="E9" s="11">
+        <v>77.3</v>
+      </c>
+      <c r="F9" s="12">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="6">
+        <v>158</v>
+      </c>
+      <c r="D10" s="10">
+        <v>3274739.94</v>
+      </c>
+      <c r="E10" s="11">
+        <v>73.5</v>
+      </c>
+      <c r="F10" s="12">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="6">
+        <v>156</v>
+      </c>
+      <c r="D11" s="10">
+        <v>3434027.51</v>
+      </c>
+      <c r="E11" s="11">
+        <v>79.3</v>
+      </c>
+      <c r="F11" s="12">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -700,72 +837,146 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ADD81C2-E051-4BAF-8CFB-BB5EEB6DBEDA}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="5">
-        <v>5000</v>
-      </c>
-      <c r="C2" s="5">
-        <v>641000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="5">
-        <v>159000</v>
-      </c>
-      <c r="C3" s="5">
-        <v>1073000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="6">
+        <v>14470</v>
+      </c>
+      <c r="D4" s="6">
+        <v>680</v>
+      </c>
+      <c r="E4" s="6">
+        <v>42</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1586</v>
+      </c>
+      <c r="G4" s="6">
+        <v>16778</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="6">
+        <v>468</v>
+      </c>
+      <c r="D5" s="6">
+        <v>658</v>
+      </c>
+      <c r="E5" s="6">
+        <v>115</v>
+      </c>
+      <c r="F5" s="6">
+        <v>123</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="5">
-        <v>940000</v>
-      </c>
-      <c r="C4" s="5">
-        <v>2412000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="5">
-        <v>2779000</v>
-      </c>
-      <c r="C5" s="5">
-        <v>5763000</v>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="6">
+        <v>17724</v>
+      </c>
+      <c r="D6" s="6">
+        <v>831</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1180</v>
+      </c>
+      <c r="G6" s="6">
+        <v>19781</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="6">
+        <v>560</v>
+      </c>
+      <c r="D7" s="6">
+        <v>942</v>
+      </c>
+      <c r="E7" s="6">
+        <v>140</v>
+      </c>
+      <c r="F7" s="6">
+        <v>112</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
 </file>
 
@@ -774,37 +985,37 @@
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="125.7109375" customWidth="1"/>
+    <col min="1" max="1" width="120.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>24</v>
+      <c r="A1" s="13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>25</v>
+      <c r="A2" s="13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>26</v>
+      <c r="A3" s="13" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>27</v>
+      <c r="A4" s="13" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>28</v>
+      <c r="A5" s="13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>29</v>
+      <c r="A6" s="13" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/task133/golden/ecl_allowance_2026Q3.xlsx
+++ b/task133/golden/ecl_allowance_2026Q3.xlsx
@@ -116,7 +116,7 @@
     <t>Scope: PL36 and PL60 loans open at close of business 30 September 2026. Loans 90 or more days past due are stage 3 and are assessed under CRM-ECL-06.</t>
   </si>
   <si>
-    <t>Stage 2: 30 or more days past due, a hardship arrangement in force on the date (start to end, both included, not from the day it is cancelled), or a behaviour score 60 or more points below origination on v4 from the month-end run on the position at the date; v3 origination scores converted as 1.12 x v3 - 18, rounded. At 30 June the June month-end run (made 1 July) supplies the scores.</t>
+    <t>Stage 2: 30 or more days past due, a hardship arrangement in force on the date (start to end, both included, not from the day it is cancelled), or a behaviour score 60 or more points below origination on v4 from the month-end run on the position at the date; v3 origination scores converted as 1.12 x v3 - 18, rounded. At 30 June the June month-end run (made 1 July) supplies the scores, and days past due are put back to close of business on 30 June: the June extract ran at 07:30 on 1 July, before CHG-26-0418, and counts each loan in arrears a day further.</t>
   </si>
   <si>
     <t>PD(k): the PLPD-2026.06 curve gives, for every loan drawn in the development window, the share defaulted by each month on book. A loan a months on book that is still open and has not defaulted takes (C(a+k) - C(a+k-1)) / S(a), where S(a) is the share of the development sample still open and never defaulted at the end of month a (1 - C(a) less the share repaid in full by then). Stage 2 PD carries the 2.4 scalar. A loan past its maturity outside stage 3 has one month remaining (3.2).</t>
@@ -125,7 +125,7 @@
     <t>EAD re-amortises the current balance over the remaining term at the contract rate; each month is discounted at the contract rate; LGD 70 per cent PL36, 76 per cent PL60; scenarios 55 / 30 / 15 per cent on multipliers 1.00 / 1.30 / 0.80 (weighted 1.06).</t>
   </si>
   <si>
-    <t>Realised loss (3.3): receipts after default to 30 September 2026 from the Collections receipts file, plus each sold account's share of the March 2026 sale (face value at cut-off x 3.85 cents), each taken at the end of the month received and discounted to the default month end at the contract rate; cured loans lose nothing.</t>
+    <t>Realised loss (3.3): receipts after default to 30 September 2026 from the Collections receipts file, plus each sold account's share of the March 2026 sale (face value at cut-off x 3.85 cents), each taken at the end of the month received and discounted to the default month end monthly at the contract rate; loans back to performing lose nothing. Collections closes a case as cured when it approves a hardship arrangement; where the arrangement was withdrawn before it started and the loan went on to write-off (agency remittances follow), the loan is measured on its receipts.</t>
   </si>
   <si>
     <t>Amounts are rounded to the nearest thousand dollars from loan-level results, so stage amounts may not add exactly.</t>

--- a/task133/golden/ecl_allowance_2026Q3.xlsx
+++ b/task133/golden/ecl_allowance_2026Q3.xlsx
@@ -26,13 +26,13 @@
     <t>Credit Risk Reporting, 9 October 2026. CRM-ECL-04 v4.2; scenarios approved 18 September 2026.</t>
   </si>
   <si>
-    <t>Collective ECL allowance (AUD)</t>
-  </si>
-  <si>
-    <t>Stage 1 allowance (AUD)</t>
-  </si>
-  <si>
-    <t>Stage 2 allowance (AUD)</t>
+    <t>Collective ECL allowance (AUD million)</t>
+  </si>
+  <si>
+    <t>Stage 1 allowance (AUD million)</t>
+  </si>
+  <si>
+    <t>Stage 2 allowance (AUD million)</t>
   </si>
   <si>
     <t>Loans in stage 1</t>
@@ -47,7 +47,7 @@
     <t>Probability-weighted PD multiplier</t>
   </si>
   <si>
-    <t>Source: loan system extract ECL_QE_BOOK at close of business 30 September 2026 (run 1 October); PLPD-2026.06 curve and development sample; Q1 FY27 scenario sheet.</t>
+    <t>Source: loan system extract ECL_QE_BOOK at close of business 30 September 2026 (run 1 October); loan record at 30 September 2026; Q1 FY27 scenario sheet.</t>
   </si>
   <si>
     <t>2023-24 defaults: share of the balance at default not recovered, at 30 September 2026 (CRM-ECL-04 3.3)</t>
@@ -119,25 +119,24 @@
     <t>Stage 2: 30 or more days past due, a hardship arrangement in force on the date (start to end, both included, not from the day it is cancelled), or a behaviour score 60 or more points below origination on v4 from the month-end run on the position at the date; v3 origination scores converted as 1.12 x v3 - 18, rounded. At 30 June the June month-end run (made 1 July) supplies the scores, and days past due are put back to close of business on 30 June: the June extract ran at 07:30 on 1 July, before CHG-26-0418, and counts each loan in arrears a day further.</t>
   </si>
   <si>
-    <t>PD(k): the PLPD-2026.06 curve gives, for every loan drawn in the development window, the share defaulted by each month on book. A loan a months on book that is still open and has not defaulted takes (C(a+k) - C(a+k-1)) / S(a), where S(a) is the share of the development sample still open and never defaulted at the end of month a (1 - C(a) less the share repaid in full by then). Stage 2 PD carries the 2.4 scalar. A loan past its maturity outside stage 3 has one month remaining (3.2).</t>
-  </si>
-  <si>
-    <t>EAD re-amortises the current balance over the remaining term at the contract rate; each month is discounted at the contract rate; LGD 70 per cent PL36, 76 per cent PL60; scenarios 55 / 30 / 15 per cent on multipliers 1.00 / 1.30 / 0.80 (weighted 1.06).</t>
-  </si>
-  <si>
-    <t>Realised loss (3.3): receipts after default to 30 September 2026 from the Collections receipts file, plus each sold account's share of the March 2026 sale (face value at cut-off x 3.85 cents), each taken at the end of the month received and discounted to the default month end monthly at the contract rate; loans back to performing lose nothing. Collections closes a case as cured when it approves a hardship arrangement; where the arrangement was withdrawn before it started and the loan went on to write-off (agency remittances follow), the loan is measured on its receipts.</t>
-  </si>
-  <si>
-    <t>Amounts are rounded to the nearest thousand dollars from loan-level results, so stage amounts may not add exactly.</t>
+    <t>PD(k): for each product and month on book (calendar months from the drawdown month), the share of the loans open and not in default at its start that defaulted in it, and the share that closed without a default, over every loan in the loan record. Each loan counts only in the months the record held it: a loan the loan system took over from the earlier platform at the October 2019 go-live counts from its first month on book after 30 September 2019, because the loans that defaulted or were repaid before then never came across. A loan at month on book a takes the default rate at a + k times the share neither defaulting nor closing in each month from a + 1 to a + k - 1. Stage 2 PD carries the 2.4 scalar. A loan past its maturity outside stage 3 has one month remaining (3.2).</t>
+  </si>
+  <si>
+    <t>EAD re-amortises the current balance over the remaining term at the contract rate; each month is discounted at the contract rate; LGD 70 per cent PL36, 76 per cent PL60; scenarios 55 / 30 / 15 per cent on multipliers 1.00 / 1.28 / 0.81 (weighted 1.0555).</t>
+  </si>
+  <si>
+    <t>Realised loss (3.3): receipts after default to 30 September 2026 from the Collections receipts file, plus each sold account's share of the March 2026 sale (face value at cut-off x 3.85 cents), each taken at the end of the month received and discounted to the default month end monthly at the contract rate; loans back to performing lose nothing. A Wirraway remittance counts against the account that held the agency reference it quotes on the day it was received, from the agency's placement report: the agency reissues the references of closed placements, and the receipts file posts a reissued reference to the account that first held it. Collections closes a case as cured when it approves a hardship arrangement; where the arrangement was withdrawn before it started and the loan was later written off or settled for less, its arrears were never made good and the loan is measured on its receipts.</t>
+  </si>
+  <si>
+    <t>Amounts are reported in AUD million to one decimal from loan-level results, so stage amounts may not add exactly.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -214,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -228,7 +227,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -569,7 +567,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4">
-        <v>13160000</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -577,7 +575,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="5">
-        <v>10563000</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -585,7 +583,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="5">
-        <v>2597000</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -682,10 +680,10 @@
       <c r="D4" s="10">
         <v>1445693.9</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="5">
         <v>67.9</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>70</v>
       </c>
     </row>
@@ -702,10 +700,10 @@
       <c r="D5" s="10">
         <v>1489194.03</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="5">
         <v>65.8</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <v>70</v>
       </c>
     </row>
@@ -722,10 +720,10 @@
       <c r="D6" s="10">
         <v>1825983.96</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="5">
         <v>70.7</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>70</v>
       </c>
     </row>
@@ -742,10 +740,10 @@
       <c r="D7" s="10">
         <v>1486050.53</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="5">
         <v>70.9</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <v>70</v>
       </c>
     </row>
@@ -757,15 +755,15 @@
         <v>18</v>
       </c>
       <c r="C8" s="6">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D8" s="10">
-        <v>3016811.56</v>
-      </c>
-      <c r="E8" s="11">
-        <v>70.4</v>
-      </c>
-      <c r="F8" s="12">
+        <v>3088797.83</v>
+      </c>
+      <c r="E8" s="5">
+        <v>70.2</v>
+      </c>
+      <c r="F8" s="11">
         <v>76</v>
       </c>
     </row>
@@ -777,15 +775,15 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D9" s="10">
-        <v>2751515.5</v>
-      </c>
-      <c r="E9" s="11">
-        <v>77.3</v>
-      </c>
-      <c r="F9" s="12">
+        <v>2770341.43</v>
+      </c>
+      <c r="E9" s="5">
+        <v>77.4</v>
+      </c>
+      <c r="F9" s="11">
         <v>76</v>
       </c>
     </row>
@@ -797,15 +795,15 @@
         <v>20</v>
       </c>
       <c r="C10" s="6">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D10" s="10">
-        <v>3274739.94</v>
-      </c>
-      <c r="E10" s="11">
-        <v>73.5</v>
-      </c>
-      <c r="F10" s="12">
+        <v>3323353.71</v>
+      </c>
+      <c r="E10" s="5">
+        <v>73.2</v>
+      </c>
+      <c r="F10" s="11">
         <v>76</v>
       </c>
     </row>
@@ -817,15 +815,15 @@
         <v>21</v>
       </c>
       <c r="C11" s="6">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D11" s="10">
-        <v>3434027.51</v>
-      </c>
-      <c r="E11" s="11">
+        <v>3460870.73</v>
+      </c>
+      <c r="E11" s="5">
         <v>79.3</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <v>76</v>
       </c>
     </row>
@@ -989,32 +987,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>36</v>
       </c>
     </row>

--- a/task133/golden/ecl_allowance_2026Q3.xlsx
+++ b/task133/golden/ecl_allowance_2026Q3.xlsx
@@ -116,7 +116,7 @@
     <t>Scope: PL36 and PL60 loans open at close of business 30 September 2026. Loans 90 or more days past due are stage 3 and are assessed under CRM-ECL-06.</t>
   </si>
   <si>
-    <t>Stage 2: 30 or more days past due, a hardship arrangement in force on the date (start to end, both included, not from the day it is cancelled), or a behaviour score 60 or more points below origination on v4 from the month-end run on the position at the date; v3 origination scores converted as 1.12 x v3 - 18, rounded. At 30 June the June month-end run (made 1 July) supplies the scores, and days past due are put back to close of business on 30 June: the June extract ran at 07:30 on 1 July, before CHG-26-0418, and counts each loan in arrears a day further.</t>
+    <t>Stage 2: 30 or more days past due, a hardship arrangement in force on the date (start to end, both included, not from the day it is cancelled), or a behaviour score 60 or more points below origination on v4 from the month-end run on the position at the date; v3 origination scores converted as 1.12 x v3 - 18, rounded. At 30 June the June month-end run (made 1 July) supplies the scores, and days past due are put back to close of business on 30 June: the June extract was read from the live system at its 07:30 run on 1 July, before CHG-26-0418 moved the job to the quarter-end day's end-of-day snapshot, so each loan in arrears reads a day further. A closed loan, one written off included, is in no stage.</t>
   </si>
   <si>
     <t>PD(k): for each product and month on book (calendar months from the drawdown month), the share of the loans open and not in default at its start that defaulted in it, and the share that closed without a default, over every loan in the loan record. Each loan counts only in the months the record held it: a loan the loan system took over from the earlier platform at the October 2019 go-live counts from its first month on book after 30 September 2019, because the loans that defaulted or were repaid before then never came across. A loan at month on book a takes the default rate at a + k times the share neither defaulting nor closing in each month from a + 1 to a + k - 1. Stage 2 PD carries the 2.4 scalar. A loan past its maturity outside stage 3 has one month remaining (3.2).</t>
@@ -125,7 +125,7 @@
     <t>EAD re-amortises the current balance over the remaining term at the contract rate; each month is discounted at the contract rate; LGD 70 per cent PL36, 76 per cent PL60; scenarios 55 / 30 / 15 per cent on multipliers 1.00 / 1.28 / 0.81 (weighted 1.0555).</t>
   </si>
   <si>
-    <t>Realised loss (3.3): receipts after default to 30 September 2026 from the Collections receipts file, plus each sold account's share of the March 2026 sale (face value at cut-off x 3.85 cents), each taken at the end of the month received and discounted to the default month end monthly at the contract rate; loans back to performing lose nothing. A Wirraway remittance counts against the account that held the agency reference it quotes on the day it was received, from the agency's placement report: the agency reissues the references of closed placements, and the receipts file posts a reissued reference to the account that first held it. Collections closes a case as cured when it approves a hardship arrangement; where the arrangement was withdrawn before it started and the loan was later written off or settled for less, its arrears were never made good and the loan is measured on its receipts.</t>
+    <t>Realised loss (3.3): for each product and quarter of default, the balance at default not recovered, summed over the quarter's defaults, as a share of their total balance at default. Recoveries are the receipts after default to 30 September 2026 in the Collections receipts file, plus each sold account's share of the March 2026 sale (face value at cut-off x 3.85 cents), each taken at the end of the month received and discounted to the default month end monthly at the contract rate. A Wirraway remittance counts against the account placed under the reference it quotes on the day it was received, from the agency's placement report; the receipts file posts it to the account first placed under that reference, an earlier account where Wirraway has reissued it. Loans back to performing lose nothing; a case Collections closed as cured on an arrangement withdrawn before it started, the loan later written off, is measured on what the loan recovered.</t>
   </si>
   <si>
     <t>Amounts are reported in AUD million to one decimal from loan-level results, so stage amounts may not add exactly.</t>

--- a/task133/golden/ecl_allowance_2026Q3.xlsx
+++ b/task133/golden/ecl_allowance_2026Q3.xlsx
@@ -116,7 +116,7 @@
     <t>Scope: PL36 and PL60 loans open at close of business 30 September 2026. Loans 90 or more days past due are stage 3 and are assessed under CRM-ECL-06.</t>
   </si>
   <si>
-    <t>Stage 2: 30 or more days past due, a hardship arrangement in force on the date (start to end, both included, not from the day it is cancelled), or a behaviour score 60 or more points below origination on v4 from the month-end run on the position at the date; v3 origination scores converted as 1.12 x v3 - 18, rounded. At 30 June the June month-end run (made 1 July) supplies the scores, and days past due are put back to close of business on 30 June: the June extract was read from the live system at its 07:30 run on 1 July, before CHG-26-0418 moved the job to the quarter-end day's end-of-day snapshot, so each loan in arrears reads a day further. A closed loan, one written off included, is in no stage.</t>
+    <t>Stage 2: 30 or more days past due, a hardship arrangement in force on the date (start to end, both included, not from the day it is cancelled), or a behaviour score 60 or more points below origination on v4 from the month-end run on the position at the date; v3 origination scores converted as 1.12 x v3 - 18, rounded. At 30 June the June month-end run (made 1 July) supplies the scores, and days past due are put back to close of business on 30 June: the June extract counts them to its run date, 1 July, so each loan in arrears reads a day further. A closed loan, one written off included, is in no stage.</t>
   </si>
   <si>
     <t>PD(k): for each product and month on book (calendar months from the drawdown month), the share of the loans open and not in default at its start that defaulted in it, and the share that closed without a default, over every loan in the loan record. Each loan counts only in the months the record held it: a loan the loan system took over from the earlier platform at the October 2019 go-live counts from its first month on book after 30 September 2019, because the loans that defaulted or were repaid before then never came across. A loan at month on book a takes the default rate at a + k times the share neither defaulting nor closing in each month from a + 1 to a + k - 1. Stage 2 PD carries the 2.4 scalar. A loan past its maturity outside stage 3 has one month remaining (3.2).</t>

--- a/task133/golden/ecl_allowance_2026Q3.xlsx
+++ b/task133/golden/ecl_allowance_2026Q3.xlsx
@@ -116,7 +116,7 @@
     <t>Scope: PL36 and PL60 loans open at close of business 30 September 2026. Loans 90 or more days past due are stage 3 and are assessed under CRM-ECL-06.</t>
   </si>
   <si>
-    <t>Stage 2: 30 or more days past due, a hardship arrangement in force on the date (start to end, both included, not from the day it is cancelled), or a behaviour score 60 or more points below origination on v4 from the month-end run on the position at the date; v3 origination scores converted as 1.12 x v3 - 18, rounded. At 30 June the June month-end run (made 1 July) supplies the scores, and days past due are put back to close of business on 30 June: the June extract counts them to its run date, 1 July, so each loan in arrears reads a day further. A closed loan, one written off included, is in no stage.</t>
+    <t>Stage 2: 30 or more days past due, a hardship arrangement in force on the date (start to end, both included, not from the day it is cancelled), or a behaviour score 60 or more points below origination on v4 from the month-end run on the position at the date; v3 origination scores converted as 1.12 x v3 - 18, rounded. At 30 June the June month end's run supplies the scores (made 1 July; for the loans that run carried forward, the rerun made 2 July), and days past due are put back to close of business on 30 June: the June extract counts them to its run date, 1 July, so each loan in arrears reads a day further. A closed loan, one written off included, is in no stage.</t>
   </si>
   <si>
     <t>PD(k): for each product and month on book (calendar months from the drawdown month), the share of the loans open and not in default at its start that defaulted in it, and the share that closed without a default, over every loan in the loan record. Each loan counts only in the months the record held it: a loan the loan system took over from the earlier platform at the October 2019 go-live counts from its first month on book after 30 September 2019, because the loans that defaulted or were repaid before then never came across. A loan at month on book a takes the default rate at a + k times the share neither defaulting nor closing in each month from a + 1 to a + k - 1. Stage 2 PD carries the 2.4 scalar. A loan past its maturity outside stage 3 has one month remaining (3.2).</t>
